--- a/tools/importer/reports/import-news.report.xlsx
+++ b/tools/importer/reports/import-news.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,13 +19,16 @@
     <t>author</t>
   </si>
   <si>
+    <t>blocks</t>
+  </si>
+  <si>
     <t>category</t>
   </si>
   <si>
     <t>path</t>
   </si>
   <si>
-    <t>publishDate</t>
+    <t>publishedDate</t>
   </si>
   <si>
     <t>status</t>
@@ -49,6 +52,9 @@
     <t>RACQ</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>News</t>
   </si>
   <si>
@@ -64,13 +70,34 @@
     <t>news</t>
   </si>
   <si>
-    <t>2026-04-01T06:44:45.023Z</t>
+    <t>2026-04-09T07:28:39.600Z</t>
   </si>
   <si>
     <t>Easter crash analysis shows trauma is often closer to home | RACQ</t>
   </si>
   <si>
     <t>https://www.racq.com.au/news/advocacy/easter-crash-analysis-shows-trauma-is-often-closer-to-home</t>
+  </si>
+  <si>
+    <t>news/racq-in-the-community/racq-helps-supercharge-energy-resilience-in-qld-communities.report.json</t>
+  </si>
+  <si>
+    <t>RACQ in the Community</t>
+  </si>
+  <si>
+    <t>news/racq-in-the-community/racq-helps-supercharge-energy-resilience-in-qld-communities</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>2026-04-09T07:28:31.715Z</t>
+  </si>
+  <si>
+    <t>RACQ helps supercharge energy resilience in Qld communities | RACQ</t>
+  </si>
+  <si>
+    <t>https://www.racq.com.au/news/racq-in-the-community/racq-helps-supercharge-energy-resilience-in-qld-communities</t>
   </si>
 </sst>
 </file>
@@ -459,20 +486,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="10" width="50" customWidth="1"/>
+    <col min="2" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,41 +530,82 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
